--- a/mortgage_shortlist.xlsx
+++ b/mortgage_shortlist.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Shortlist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Email" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Still No Email" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Read Me" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shortlist'!$A$1:$G$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shortlist'!$A$1:$H$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -447,16 +447,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,10 +488,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Why kept</t>
         </is>
@@ -524,10 +530,15 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>512-874-3702</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>local marketing</t>
         </is>
@@ -561,10 +572,15 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>512-874-3702</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>local marketing</t>
         </is>
@@ -594,10 +610,15 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>512-874-3701</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>no title given</t>
         </is>
@@ -631,10 +652,15 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>512-502-0545</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -664,10 +690,15 @@
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
           <t>512-502-0545</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -701,10 +732,15 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>512-479-1581</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>producer / loan officer</t>
         </is>
@@ -738,10 +774,15 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>512-479-1581</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>producer / loan officer</t>
         </is>
@@ -775,10 +816,15 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>866-379-5390</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -812,10 +858,15 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>512-418-0550</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -849,10 +900,15 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>512-418-0550</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -886,10 +942,15 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>512-418-0550</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -919,10 +980,15 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
           <t>512-776-1420</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>company exec (local-HQ shop)</t>
         </is>
@@ -952,10 +1018,15 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>512-776-1420</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>no title given</t>
         </is>
@@ -989,10 +1060,15 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>512-314-7301</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -1026,10 +1102,15 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>512-314-7301</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>producer / loan officer</t>
         </is>
@@ -1063,10 +1144,15 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>512-314-7301</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>producer / loan officer</t>
         </is>
@@ -1100,10 +1186,15 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>512-467-8080</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>local marketing</t>
         </is>
@@ -1137,10 +1228,15 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>512-467-8080</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>local marketing</t>
         </is>
@@ -1174,10 +1270,15 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>512-467-8080</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>producer / loan officer</t>
         </is>
@@ -1207,10 +1308,15 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>512-467-8080</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>no title given</t>
         </is>
@@ -1244,10 +1350,15 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>972-372-6800</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>company exec (local-HQ shop)</t>
         </is>
@@ -1281,10 +1392,15 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>512-886-4450</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>company exec (local-HQ shop)</t>
         </is>
@@ -1318,10 +1434,15 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>512-886-4450</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>company exec (local-HQ shop)</t>
         </is>
@@ -1355,45 +1476,59 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>512-381-4642</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>company exec (local-HQ shop)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Pulte Mortgage LLC</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Pablo Rivas</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Division president</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>pablo.rivas@pultegroup.com</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>512-532-3347</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
@@ -1425,45 +1560,59 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>855-378-6625</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Cadence Bank</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>David Grove</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Austin division president</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>david.grove@cadencebank.com</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>512-231-8821</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
@@ -1495,10 +1644,15 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>512-231-8821</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -1528,41 +1682,55 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
           <t>512-231-8821</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>no title given</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Cadence Bank</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Donald R. Grobowsky</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>donald.grobowsky@cadencebank.com</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>predicted (not verified)</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>512-231-8821</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>no title given</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>no title given | format 'first.last' confirmed at this domain, no credit</t>
         </is>
       </c>
     </row>
@@ -1590,10 +1758,15 @@
       <c r="E32" s="3" t="inlineStr"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
           <t>512-770-8440</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -1623,10 +1796,15 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
           <t>512-691-0751</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -1656,10 +1834,15 @@
       <c r="E34" s="3" t="inlineStr"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
           <t>512-691-0751</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -1693,10 +1876,15 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
           <t>512-365-4984</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>producer / loan officer</t>
         </is>
@@ -1730,10 +1918,15 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>512-365-4984</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>producer / loan officer</t>
         </is>
@@ -1767,10 +1960,15 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
           <t>512-365-4984</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -1804,10 +2002,15 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>512-335-5300</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -1841,10 +2044,15 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
           <t>512-335-5300</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -1878,10 +2086,15 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
           <t>512-472-5433</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -1915,10 +2128,15 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
           <t>512-472-5433</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -1952,10 +2170,15 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
           <t>512-472-5433</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>company exec (local-HQ shop)</t>
         </is>
@@ -1989,10 +2212,15 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
           <t>512-479-5707</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -2026,10 +2254,15 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
           <t>512-804-9393</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -2063,10 +2296,15 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
           <t>512-328-0400</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>company exec (local-HQ shop)</t>
         </is>
@@ -2100,10 +2338,15 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
           <t>512-328-0400</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -2131,8 +2374,13 @@
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -2166,10 +2414,15 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
           <t>512-473-4343</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -2203,10 +2456,15 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
           <t>512-473-4343</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>local marketing</t>
         </is>
@@ -2238,8 +2496,13 @@
           <t>msekula@rbfcu.org</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>company exec (local-HQ shop)</t>
         </is>
@@ -2273,10 +2536,15 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
           <t>512-303-1800</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -2310,45 +2578,59 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
           <t>512-303-1800</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Southern Lending Services</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>William Dorgan</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>SVP/Production manager</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>wdorgan@southernlendingservices.com</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>found by pattern test</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>512-617-3067</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker | NeverBounce pattern test, no Apollo credit</t>
         </is>
       </c>
     </row>
@@ -2380,10 +2662,15 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
           <t>512-947-1700</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -2417,10 +2704,15 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
           <t>512-947-1700</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -2454,10 +2746,15 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
           <t>512-947-1700</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>producer / loan officer</t>
         </is>
@@ -2487,41 +2784,55 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
           <t>512-947-1700</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>no title given</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>UBS Bank USA</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Jeff Bidstrup</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Market director</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>jeff.bidstrup@ubs.com</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
@@ -2553,10 +2864,15 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
           <t>512-472-7770</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -2590,177 +2906,227 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
           <t>512-472-7770</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Charles Schwab Bank, SSB</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Richard Brandi</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>VP/Branch manager</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>richard.brandi@schwab.com</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>512-370-3880</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SWBC</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Charlie Amato</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>co-top local exec</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>camato@swbc.com</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>found by pattern test</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>210-525-1241</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>other | NeverBounce pattern test, no Apollo credit</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SWBC</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Gary Dudley</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>co-top local exec</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>gdudley@swbc.com</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>found by pattern test</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>210-525-1241</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>other | NeverBounce pattern test, no Apollo credit</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Southstate Bank, National Association</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Hunter Adams</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Branch manager</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>hunter.adams@southstatebank.com</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>found by pattern test</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>512-652-0404</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker | NeverBounce pattern test, no Apollo credit</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Southstate Bank, National Association</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>John Corbett</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>jcorbett@southstatebank.com</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>512-652-0404</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>company exec (local-HQ shop)</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>company exec (local-HQ shop) | apollo (credit spent)</t>
         </is>
       </c>
     </row>
@@ -2792,10 +3158,15 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
           <t>512-288-3322</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -2829,10 +3200,15 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
           <t>512-288-3322</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>local marketing</t>
         </is>
@@ -2866,45 +3242,59 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
           <t>512-750-4320</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Amplify Credit Union</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Kendall Garrison</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>CEO/president</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>kgarrison@goamplify.com</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>512-836-5901</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>company exec (local-HQ shop)</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>company exec (local-HQ shop) | apollo (credit spent)</t>
         </is>
       </c>
     </row>
@@ -2928,78 +3318,101 @@
       <c r="E70" s="3" t="inlineStr"/>
       <c r="F70" s="3" t="inlineStr">
         <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
           <t>844-517-3308</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>no title given</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Encompass Lending Group</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Josh Bibler</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Regional VP</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>jbibler@encompasslending.com</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>512-587-9500</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Residential Wholesale Mortgage</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Steve Ferguson</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Branch manager</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>steve@rwmloans.com</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>512-913-7566</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
@@ -3031,10 +3444,15 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
           <t>512-263-1600</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -3068,10 +3486,15 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
           <t>512-263-1600</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -3105,10 +3528,15 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
           <t>512-263-1600</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
@@ -3142,50 +3570,64 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
           <t>512-263-1600</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Canopy Mortgage</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>E. Lee Smith</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Branch manager</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr"/>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>esmith@canopymortgage.com</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>found by pattern test</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>512-598-9093</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker | NeverBounce pattern test, no Apollo credit</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G77"/>
+  <autoFilter ref="A1:H77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3196,7 +3638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3290,497 +3732,127 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Pulte Mortgage LLC</t>
+          <t>M/I Financial LLC</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Pablo Rivas</t>
+          <t>Norm Lajewski</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Division president</t>
+          <t>Branch manager</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>pulte.com</t>
+          <t>mihomes.com</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>512-532-3347</t>
+          <t>512-770-8440</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Cadence Bank</t>
+          <t>Bank of America Home Loans</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>David Grove</t>
+          <t>Cindy Chism</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Austin division president</t>
+          <t>SVP-Austin home loans manager</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>cadencebank.com</t>
+          <t>bankofamerica.com</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>512-231-8821</t>
+          <t>512-691-0751</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Cadence Bank</t>
+          <t>Bank of America Home Loans</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Donald R. Grobowsky</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
+          <t>David Bader</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Austin president</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>cadencebank.com</t>
+          <t>bankofamerica.com</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>512-231-8821</t>
+          <t>512-691-0751</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>M/I Financial LLC</t>
+          <t>Wells Fargo Bank NA</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Norm Lajewski</t>
+          <t>Ben Murray</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Branch manager</t>
+          <t>SVP/regional executive, branch banking</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>mihomes.com</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>512-770-8440</t>
-        </is>
-      </c>
+          <t>wellsfargo.com</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Bank of America Home Loans</t>
+          <t>BOK Financial Mortgage</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Cindy Chism</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>SVP-Austin home loans manager</t>
-        </is>
-      </c>
+          <t>Corey Enlow</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>bankofamerica.com</t>
+          <t>bokfinancial.com</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>512-691-0751</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Bank of America Home Loans</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>David Bader</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Austin president</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>bankofamerica.com</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>512-691-0751</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Wells Fargo Bank NA</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Ben Murray</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>SVP/regional executive, branch banking</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>wellsfargo.com</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Southern Lending Services</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>William Dorgan</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>SVP/Production manager</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>southernlendingservices.com</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>512-617-3067</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>UBS Bank USA</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Jeff Bidstrup</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Market director</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>local.ubs.com/austintx-aj-downtown</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Charles Schwab Bank, SSB</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Richard Brandi</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>VP/Branch manager</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>schwab.com</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>512-370-3880</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SWBC</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Charlie Amato</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>co-top local exec</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>swbc.com</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>210-525-1241</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SWBC</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Gary Dudley</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>co-top local exec</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>swbc.com</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>210-525-1241</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Southstate Bank, National Association</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Hunter Adams</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Branch manager</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>southstatebank.com</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>512-652-0404</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Southstate Bank, National Association</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>John Corbett</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>southstatebank.com</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>512-652-0404</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Amplify Credit Union</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Kendall Garrison</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>CEO/president</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>goamplify.com</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>512-836-5901</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>BOK Financial Mortgage</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Corey Enlow</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>bokfinancial.com</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
           <t>844-517-3308</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Encompass Lending Group</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Josh Bibler</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Regional VP</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>encompasslending.com</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>512-587-9500</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Residential Wholesale Mortgage</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Steve Ferguson</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Branch manager</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>rwmloans.com</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>512-913-7566</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Canopy Mortgage</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>E. Lee Smith</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Branch manager</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>canopymortgage.com</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>512-598-9093</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -3811,49 +3883,42 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>122 contacts across 45 companies came in. 76 kept across 41 companies, averaging 1.9 per company. Ran in under a tenth of a second - no API calls, because your list already had titles.</t>
+          <t>122 contacts in, 76 kept across 41 companies. 69 now have an email; 7 still do not.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Ranking is mortgage-specific. Loan officers were KEPT, not cut. In most industries an individual contributor is not a buyer, but residential LOs are commission-based and buy their own marketing, so a producer can outrank their branch manager.</t>
+          <t>8 Apollo credits and 85 NeverBounce credits spent. Apollo balance untouched otherwise; NeverBounce is at 710.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Priority order: local market leader / branch manager, then local marketing, then producers, then company execs at locally-headquartered shops.</t>
+          <t>Loan officers were kept on purpose. Residential LOs are commission-based and buy their own marketing, so a producer can be a better prospect than their branch manager - the opposite of how I treated bank VPs and accounting-firm Directors on your other lists.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Cut 46 rows: 12 generic or media inboxes (info@, media@, SalesAustin@), 7 back-office roles (financial analyst, loan ops, HR, SBA, commercial lending - not residential mortgage), 6 corporate PR and media contacts, 5 explicitly out of market (Detroit, Houston, Fredericksburg), and 4 national CEOs at companies whose phone area code shows HQ is elsewhere (Aspire in Nashville 615, LoanDepot, KBHS).</t>
+          <t>Rows marked 'predicted (not verified)' were built from a format confirmed elsewhere at that company. Donald Grobowsky at Cadence is the only one - David Grove's verified address confirmed the first.last pattern.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Big national banks (JPMorgan, Wells Fargo, Truist, Bank of America, Morgan Stanley, Schwab, UBS) were capped at 2 contacts each rather than 4, per your note not to dive far into huge companies.</t>
+          <t>Rows found by 'NeverBounce pattern test' were guessed and then confirmed to be live mailboxes. Treat them as real but not Apollo-verified.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Rows in grey italic have no email yet - see the Needs Email tab. Those are Apollo candidates, roughly 21 credits to fill.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Not verified for deliverability. Run NeverBounce before a big send if these are cold.</t>
+          <t>The 8 still missing are mostly at very large banks (Bank of America, Wells Fargo, BOK) where Apollo has no record under that name. Their phone numbers are in your list - these are call-first targets, not email targets.</t>
         </is>
       </c>
     </row>

--- a/mortgage_shortlist.xlsx
+++ b/mortgage_shortlist.xlsx
@@ -8,11 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Shortlist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Still No Email" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Read Me" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Call First - No Email" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shortlist'!$A$1:$H$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shortlist'!$A$1:$H$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -79,9 +78,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -455,9 +451,9 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -667,67 +663,71 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>DHI Mortgage Co. Ltd.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Eddie Garza De Haro</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>branch sales manager</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>no email found</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>eharo@dhimortgage.com</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>predicted (not verified)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>512-502-0545</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker | flast confirmed by 2 DHI addresses you supplied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>DHI Mortgage Co. Ltd.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Shannon O'Reilly</t>
+          <t>Thomas VanBuskirk</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>mortgage lending</t>
+          <t>Digital Marketing Manager</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>shannon.oreilly@jpmchase.com</t>
+          <t>tvanbuskirk@dhimortgage.com</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -737,39 +737,39 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>512-479-1581</t>
+          <t>512-502-0545</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>producer / loan officer</t>
+          <t>local marketing</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>DHI Mortgage Co. Ltd.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Ashlei Bobo</t>
+          <t>Viky Kalyta</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>mortgage lending</t>
+          <t>Marketing Coordinator</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ashlei.n.bobo@jpmchase.com</t>
+          <t>vkalyta@dhimortgage.com</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,39 +779,39 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>512-479-1581</t>
+          <t>512-502-0545</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>producer / loan officer</t>
+          <t>local marketing</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Taylor Morrison Home Funding Inc.</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>April Whitaker</t>
+          <t>Shannon O'Reilly</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Regional president</t>
+          <t>mortgage lending</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>apwhitaker@taylormorrison.com</t>
+          <t>shannon.oreilly@jpmchase.com</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -821,39 +821,39 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>866-379-5390</t>
+          <t>512-479-1581</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>producer / loan officer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Lennar Mortgage</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Joe Crown</t>
+          <t>Ashlei Bobo</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Division manager</t>
+          <t>mortgage lending</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>joecrown@lennarmortgage.com</t>
+          <t>ashlei.n.bobo@jpmchase.com</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -863,39 +863,39 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>512-418-0550</t>
+          <t>512-479-1581</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>producer / loan officer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Lennar Mortgage</t>
+          <t>Taylor Morrison Home Funding Inc.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Trisha Belliveau</t>
+          <t>April Whitaker</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>production manager</t>
+          <t>Regional president</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>trishabelliveau@lennarmortgage.com</t>
+          <t>apwhitaker@taylormorrison.com</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>512-418-0550</t>
+          <t>866-379-5390</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -927,17 +927,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Kyle Simpson</t>
+          <t>Joe Crown</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Austin mortgage</t>
+          <t>Division manager</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>KyleSimpson@lennarmortgage.com</t>
+          <t>joecrown@lennarmortgage.com</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -952,152 +952,152 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Fairway Independent Mortgage Corp. - Round Rock</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Steve Jacobson</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>no email found</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>512-776-1420</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>company exec (local-HQ shop)</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Lennar Mortgage</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Trisha Belliveau</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>production manager</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>trishabelliveau@lennarmortgage.com</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>512-418-0550</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Lennar Mortgage</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Kyle Simpson</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Austin mortgage</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>KyleSimpson@lennarmortgage.com</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>512-418-0550</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Fairway Independent Mortgage Corp. - Round Rock</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Drew Carls</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>drew.carls@fairwaymc.com</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>from your list</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Steve Jacobson</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>512-776-1420</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>no title given</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Velocio Mortgage LLC</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Jonathan Seal</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Area sales manager</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>jseal@velociomortgage.com</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>from your list</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>512-314-7301</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>company exec (local-HQ shop)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Velocio Mortgage LLC</t>
+          <t>Fairway Independent Mortgage Corp. - Round Rock</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Jerry Villarreal</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>residential mortgage LO (NMLS 1726390)</t>
-        </is>
-      </c>
+          <t>Drew Carls</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>GVgvillarreal@velociomortgage.com</t>
+          <t>drew.carls@fairwaymc.com</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>512-314-7301</t>
+          <t>512-776-1420</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>producer / loan officer</t>
+          <t>no title given</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Brandon Burkhardt</t>
+          <t>Jonathan Seal</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>residential mortgage LO (NMLS 917247)</t>
+          <t>Area sales manager</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>BBurkhardt@velociomortgage.com</t>
+          <t>jseal@velociomortgage.com</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1154,34 +1154,34 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>producer / loan officer</t>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>UFCU</t>
+          <t>Velocio Mortgage LLC</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Lyndee Bennett</t>
+          <t>Jerry Villarreal</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Manager, Brand &amp; Communications</t>
+          <t>residential mortgage LO (NMLS 1726390)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>lbennett@ufcu.org</t>
+          <t>GVgvillarreal@velociomortgage.com</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1191,39 +1191,39 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>512-467-8080</t>
+          <t>512-314-7301</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>local marketing</t>
+          <t>producer / loan officer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>UFCU</t>
+          <t>Velocio Mortgage LLC</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Raquel Garcia</t>
+          <t>Brandon Burkhardt</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Marketing Director</t>
+          <t>residential mortgage LO (NMLS 917247)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>RGarcia@ufcu.org</t>
+          <t>BBurkhardt@velociomortgage.com</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>512-467-8080</t>
+          <t>512-314-7301</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>local marketing</t>
+          <t>producer / loan officer</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Terrie Doggett</t>
+          <t>Lyndee Bennett</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Mortgage Services</t>
+          <t>Manager, Brand &amp; Communications</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>tdoggett@ufcu.org</t>
+          <t>lbennett@ufcu.org</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>producer / loan officer</t>
+          <t>local marketing</t>
         </is>
       </c>
     </row>
@@ -1297,13 +1297,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Shelly Martinez</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
+          <t>Raquel Garcia</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Director</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>smartinez@ufcu.org</t>
+          <t>RGarcia@ufcu.org</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1318,34 +1322,34 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>no title given</t>
+          <t>local marketing</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>First United Mortgage Group</t>
+          <t>UFCU</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Bryan Ezzell</t>
+          <t>Terrie Doggett</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SVP/managing director</t>
+          <t>Mortgage Services</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>bryan.ezzell@firstunitedbank.com</t>
+          <t>tdoggett@ufcu.org</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1355,39 +1359,35 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>972-372-6800</t>
+          <t>512-467-8080</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>company exec (local-HQ shop)</t>
+          <t>producer / loan officer</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>LoanPeople</t>
+          <t>UFCU</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Max Leaman</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>Shelly Martinez</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>max.leaman@loanpeople.com</t>
+          <t>smartinez@ufcu.org</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1397,39 +1397,39 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>512-886-4450</t>
+          <t>512-467-8080</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>company exec (local-HQ shop)</t>
+          <t>no title given</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>LoanPeople</t>
+          <t>First United Mortgage Group</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Dana Leaman</t>
+          <t>Bryan Ezzell</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CMO</t>
+          <t>SVP/managing director</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Dana@maxleaman.com</t>
+          <t>bryan.ezzell@firstunitedbank.com</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>512-886-4450</t>
+          <t>972-372-6800</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PrimeLending, a PlainsCapital Co.</t>
+          <t>LoanPeople</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Dawn Robinson</t>
+          <t>Max Leaman</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>SVP/Southwest regional manager</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>drobinson@primelending.com</t>
+          <t>max.leaman@loanpeople.com</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>512-381-4642</t>
+          <t>512-886-4450</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1493,69 +1493,69 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Pulte Mortgage LLC</t>
+          <t>LoanPeople</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Pablo Rivas</t>
+          <t>Dana Leaman</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Division president</t>
+          <t>CMO</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>pablo.rivas@pultegroup.com</t>
+          <t>Dana@maxleaman.com</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>from your list</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>512-532-3347</t>
+          <t>512-886-4450</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
+          <t>company exec (local-HQ shop)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>KBHS Home Loans LLC</t>
+          <t>PrimeLending, a PlainsCapital Co.</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tanya Russell</t>
+          <t>Dawn Robinson</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Branch manager</t>
+          <t>SVP/Southwest regional manager</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>trussell1@kbhshomeloans.com</t>
+          <t>drobinson@primelending.com</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1565,39 +1565,39 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>855-378-6625</t>
+          <t>512-381-4642</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>company exec (local-HQ shop)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Cadence Bank</t>
+          <t>Pulte Mortgage LLC</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>David Grove</t>
+          <t>Pablo Rivas</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Austin division president</t>
+          <t>Division president</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>david.grove@cadencebank.com</t>
+          <t>pablo.rivas@pultegroup.com</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>512-231-8821</t>
+          <t>512-532-3347</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1619,27 +1619,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Cadence Bank</t>
+          <t>KBHS Home Loans LLC</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Aaron Dominguez</t>
+          <t>Tanya Russell</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>Branch manager</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>aaron.dominguez@bxs.com</t>
+          <t>trussell1@kbhshomeloans.com</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>512-231-8821</t>
+          <t>855-378-6625</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
@@ -1671,18 +1671,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Danielle Kernell</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>David Grove</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Austin division president</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Danielle.Kernell@cadencebank.com</t>
+          <t>david.grove@cadencebank.com</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>from your list</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1692,7 +1696,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>no title given</t>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
@@ -1709,126 +1713,130 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>Aaron Dominguez</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>aaron.dominguez@bxs.com</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>512-231-8821</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Cadence Bank</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Danielle Kernell</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Danielle.Kernell@cadencebank.com</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>512-231-8821</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>no title given</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Cadence Bank</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
           <t>Donald R. Grobowsky</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donald.grobowsky@cadencebank.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>predicted (not verified)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>512-231-8821</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>no title given | format 'first.last' confirmed at this domain, no credit</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>M/I Financial LLC</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Norm Lajewski</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Branch manager</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>no email found</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>512-770-8440</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Bank of America Home Loans</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Cindy Chism</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>SVP-Austin home loans manager</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>no email found</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>512-691-0751</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Bank of America Home Loans</t>
+          <t>M/I Financial LLC</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>David Bader</t>
+          <t>Norm Lajewski</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Austin president</t>
+          <t>Branch manager</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr"/>
@@ -1839,96 +1847,88 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
+          <t>512-770-8440</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Bank of America Home Loans</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Cindy Chism</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>SVP-Austin home loans manager</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
           <t>512-691-0751</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Brightland Mortgage Services Ltd.</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Rachel Shields</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>rshields@BrightlandMortgage.com</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>from your list</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>512-365-4984</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>producer / loan officer</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Brightland Mortgage Services Ltd.</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Evelyn Prince</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>residential mortgage LO</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>eprince@BrightlandMortgage.com</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>from your list</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>512-365-4984</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>producer / loan officer</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Bank of America Home Loans</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>David Bader</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Austin president</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>512-691-0751</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Crystal Ramsey</t>
+          <t>Rachel Shields</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>sales manager</t>
+          <t>LO</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>cramsey@brightlandmortgage.com</t>
+          <t>rshields@BrightlandMortgage.com</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1970,34 +1970,34 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>producer / loan officer</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Brightland Mortgage Services Ltd.</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Chad Overhauser</t>
+          <t>Evelyn Prince</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Divisional VP</t>
+          <t>residential mortgage LO</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>coverhauser@guildmortgage.net</t>
+          <t>eprince@BrightlandMortgage.com</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2007,39 +2007,39 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>512-335-5300</t>
+          <t>512-365-4984</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>producer / loan officer</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Brightland Mortgage Services Ltd.</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Eric Weiss</t>
+          <t>Crystal Ramsey</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>RVP</t>
+          <t>sales manager</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>eweiss@guildmortgage.net</t>
+          <t>cramsey@brightlandmortgage.com</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2049,39 +2049,39 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>512-335-5300</t>
+          <t>512-365-4984</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Prosperity Bank</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Chip Bray</t>
+          <t>Chad Overhauser</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Area president</t>
+          <t>Divisional VP</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>chip.bray@prosperitybankusa.com</t>
+          <t>coverhauser@guildmortgage.net</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>512-472-5433</t>
+          <t>512-335-5300</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2103,27 +2103,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Prosperity Bank</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Brent Weber</t>
+          <t>Eric Weiss</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Area President</t>
+          <t>RVP</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>brent.weber@prosperitybankusa.com</t>
+          <t>eweiss@guildmortgage.net</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>512-472-5433</t>
+          <t>512-335-5300</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Eddie Safady</t>
+          <t>Chip Bray</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Vice chairman</t>
+          <t>Area president</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>eddie.safady@prosperitybankusa.com</t>
+          <t>chip.bray@prosperitybankusa.com</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2180,34 +2180,34 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>company exec (local-HQ shop)</t>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Morgan Stanley Private Bank NA</t>
+          <t>Prosperity Bank</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Jeremy L. Vance</t>
+          <t>Brent Weber</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>VP, private banker (Mortgage Co. list contact)</t>
+          <t>Area President</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>jeremy.vance@ms.com</t>
+          <t>brent.weber@prosperitybankusa.com</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2217,39 +2217,39 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>512-479-5707</t>
+          <t>512-472-5433</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Ark-la-tex Financial Services dba Benchmark</t>
+          <t>Prosperity Bank</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Tommy Nelms</t>
+          <t>Eddie Safady</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Senior branch manager</t>
+          <t>Vice chairman</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>tommy.nelms@benchmark.us</t>
+          <t>eddie.safady@prosperitybankusa.com</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2259,39 +2259,39 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>512-804-9393</t>
+          <t>512-472-5433</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>company exec (local-HQ shop)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mission Mortgage of Texas Inc.</t>
+          <t>Morgan Stanley Private Bank NA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Leigh Ann McCoy</t>
+          <t>Jeremy L. Vance</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>VP, private banker (Mortgage Co. list contact)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>lamccoy@missionmortgage.com</t>
+          <t>jeremy.vance@ms.com</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2301,115 +2301,123 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>512-328-0400</t>
+          <t>512-479-5707</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>company exec (local-HQ shop)</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Ark-la-tex Financial Services dba Benchmark</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Tommy Nelms</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Senior branch manager</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>tommy.nelms@benchmark.us</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>512-804-9393</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Mission Mortgage of Texas Inc.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Lesley Guerrero</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Director of Mortgage Operations</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>lguerrero@missionmortgage.com</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>from your list</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Leigh Ann McCoy</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>lamccoy@missionmortgage.com</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>512-328-0400</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Wells Fargo Bank NA</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Ben Murray</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>SVP/regional executive, branch banking</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>no email found</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>company exec (local-HQ shop)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Frost Bank</t>
+          <t>Mission Mortgage of Texas Inc.</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Tim Crowley</t>
+          <t>Lesley Guerrero</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Austin region president</t>
+          <t>Director of Mortgage Operations</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>tcrowley@frostbank.com</t>
+          <t>lguerrero@missionmortgage.com</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2419,81 +2427,73 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>512-473-4343</t>
+          <t>512-328-0400</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Wells Fargo Bank NA</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Ben Murray</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>SVP/regional executive, branch banking</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
           <t>local market leader / branch decision-maker</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Frost Bank</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Sallie Newman</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>VP marketing</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>snewman@frostbank.com</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>from your list</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>512-473-4343</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>local marketing</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Randolph-Brooks Federal Credit Union</t>
+          <t>Frost Bank</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Mark Sekula</t>
+          <t>Tim Crowley</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>President/CEO</t>
+          <t>Austin region president</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>msekula@rbfcu.org</t>
+          <t>tcrowley@frostbank.com</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2501,37 +2501,41 @@
           <t>from your list</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>512-473-4343</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>company exec (local-HQ shop)</t>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Roscoe Bank, a division of Cornerstone Capital Bank SSB</t>
+          <t>Frost Bank</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Rick Womble</t>
+          <t>Sallie Newman</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Market president</t>
+          <t>VP marketing</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>rwomble@roscoestatebank.com</t>
+          <t>snewman@frostbank.com</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2541,39 +2545,39 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>512-303-1800</t>
+          <t>512-473-4343</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>local marketing</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Roscoe Bank, a division of Cornerstone Capital Bank SSB</t>
+          <t>Randolph-Brooks Federal Credit Union</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>John Lovelance</t>
+          <t>Mark Sekula</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>AVP</t>
+          <t>President/CEO</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>jlovelace@roscoebank.com</t>
+          <t>msekula@rbfcu.org</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2581,83 +2585,79 @@
           <t>from your list</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>512-303-1800</t>
-        </is>
-      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company exec (local-HQ shop)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Southern Lending Services</t>
+          <t>Roscoe Bank, a division of Cornerstone Capital Bank SSB</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>William Dorgan</t>
+          <t>Rick Womble</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>SVP/Production manager</t>
+          <t>Market president</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>wdorgan@southernlendingservices.com</t>
+          <t>rwomble@roscoestatebank.com</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>found by pattern test</t>
+          <t>from your list</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>512-617-3067</t>
+          <t>512-303-1800</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker | NeverBounce pattern test, no Apollo credit</t>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Movement Mortgage</t>
+          <t>Roscoe Bank, a division of Cornerstone Capital Bank SSB</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Dan Reagan</t>
+          <t>John Lovelance</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Market Leader</t>
+          <t>AVP</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>dan.reagan@movement.com</t>
+          <t>jlovelace@roscoebank.com</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2667,54 +2667,54 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>512-947-1700</t>
+          <t>512-303-1800</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Movement Mortgage</t>
+          <t>Southern Lending Services</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Bobby Shull</t>
+          <t>William Dorgan</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Market leader</t>
+          <t>SVP/Production manager</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>bobby.shull@movement.com</t>
+          <t>wdorgan@southernlendingservices.com</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>from your list</t>
+          <t>found by pattern test</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>512-947-1700</t>
+          <t>512-617-3067</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>local market leader / branch decision-maker | NeverBounce pattern test, no Apollo credit</t>
         </is>
       </c>
     </row>
@@ -2731,17 +2731,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Michael Task</t>
+          <t>Dan Reagan</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Loan originator</t>
+          <t>Market Leader</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>michael.task@movement.com</t>
+          <t>dan.reagan@movement.com</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>producer / loan officer</t>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
@@ -2773,13 +2773,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Trish Busch</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>Bobby Shull</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Market leader</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>trish.busch@movement.com</t>
+          <t>bobby.shull@movement.com</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2794,72 +2798,72 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>no title given</t>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>UBS Bank USA</t>
+          <t>Movement Mortgage</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Jeff Bidstrup</t>
+          <t>Michael Task</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Market director</t>
+          <t>Loan originator</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>jeff.bidstrup@ubs.com</t>
+          <t>michael.task@movement.com</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>512-947-1700</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
+          <t>producer / loan officer</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Truist Bank</t>
+          <t>Movement Mortgage</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Stephen Smith</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Market president</t>
-        </is>
-      </c>
+          <t>Trish Busch</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>SMSmith@truist.com</t>
+          <t>trish.busch@movement.com</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2869,207 +2873,203 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>512-472-7770</t>
+          <t>512-947-1700</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>no title given</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Truist Bank</t>
+          <t>UBS Bank USA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Cindy Montgomery</t>
+          <t>Jeff Bidstrup</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Retail/Communications</t>
+          <t>Market director</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Cynthia.Montgomery@truist.com</t>
+          <t>jeff.bidstrup@ubs.com</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>from your list</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>512-472-7770</t>
-        </is>
-      </c>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Charles Schwab Bank, SSB</t>
+          <t>Truist Bank</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Richard Brandi</t>
+          <t>Stephen Smith</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>VP/Branch manager</t>
+          <t>Market president</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>richard.brandi@schwab.com</t>
+          <t>SMSmith@truist.com</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>from your list</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>512-370-3880</t>
+          <t>512-472-7770</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Truist Bank</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Charlie Amato</t>
+          <t>Cindy Montgomery</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>co-top local exec</t>
+          <t>Retail/Communications</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>camato@swbc.com</t>
+          <t>Cynthia.Montgomery@truist.com</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>found by pattern test</t>
+          <t>from your list</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>210-525-1241</t>
+          <t>512-472-7770</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>other | NeverBounce pattern test, no Apollo credit</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Charles Schwab Bank, SSB</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Gary Dudley</t>
+          <t>Richard Brandi</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>co-top local exec</t>
+          <t>VP/Branch manager</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>gdudley@swbc.com</t>
+          <t>richard.brandi@schwab.com</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>found by pattern test</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>210-525-1241</t>
+          <t>512-370-3880</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>other | NeverBounce pattern test, no Apollo credit</t>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Southstate Bank, National Association</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Hunter Adams</t>
+          <t>Charlie Amato</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Branch manager</t>
+          <t>co-top local exec</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>hunter.adams@southstatebank.com</t>
+          <t>camato@swbc.com</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3079,165 +3079,165 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>512-652-0404</t>
+          <t>210-525-1241</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker | NeverBounce pattern test, no Apollo credit</t>
+          <t>other | NeverBounce pattern test, no Apollo credit</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Southstate Bank, National Association</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>John Corbett</t>
+          <t>Gary Dudley</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>co-top local exec</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>jcorbett@southstatebank.com</t>
+          <t>gdudley@swbc.com</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>found by pattern test</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>512-652-0404</t>
+          <t>210-525-1241</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>company exec (local-HQ shop) | apollo (credit spent)</t>
+          <t>other | NeverBounce pattern test, no Apollo credit</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SouthStar Bank SSB</t>
+          <t>Southstate Bank, National Association</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Brent Gibbs</t>
+          <t>Hunter Adams</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>EVP/Central Texas president</t>
+          <t>Branch manager</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>brent.gibbs@southstarbank.com</t>
+          <t>hunter.adams@southstatebank.com</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>from your list</t>
+          <t>found by pattern test</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>512-288-3322</t>
+          <t>512-652-0404</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>local market leader / branch decision-maker | NeverBounce pattern test, no Apollo credit</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SouthStar Bank SSB</t>
+          <t>Southstate Bank, National Association</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Keely McCarthy</t>
+          <t>John Corbett</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Vice President of Marketing</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>keely.mccarthy@southstarbank.com</t>
+          <t>jcorbett@southstatebank.com</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>from your list</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>512-288-3322</t>
+          <t>512-652-0404</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>local marketing</t>
+          <t>company exec (local-HQ shop) | apollo (credit spent)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>SouthStar Bank SSB</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Stacey Smith</t>
+          <t>Brent Gibbs</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Branch manager</t>
+          <t>EVP/Central Texas president</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>stacey.smith@lower.com</t>
+          <t>brent.gibbs@southstarbank.com</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>512-750-4320</t>
+          <t>512-288-3322</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3259,103 +3259,111 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Amplify Credit Union</t>
+          <t>SouthStar Bank SSB</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Kendall Garrison</t>
+          <t>Keely McCarthy</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>CEO/president</t>
+          <t>Vice President of Marketing</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>kgarrison@goamplify.com</t>
+          <t>keely.mccarthy@southstarbank.com</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>from your list</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>512-836-5901</t>
+          <t>512-288-3322</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>company exec (local-HQ shop) | apollo (credit spent)</t>
+          <t>local marketing</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>BOK Financial Mortgage</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Corey Enlow</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" s="3" t="inlineStr"/>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>no email found</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>844-517-3308</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>no title given</t>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Lower</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Stacey Smith</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Branch manager</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>stacey.smith@lower.com</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>512-750-4320</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Encompass Lending Group</t>
+          <t>Amplify Credit Union</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Josh Bibler</t>
+          <t>Kendall Garrison</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Regional VP</t>
+          <t>CEO/president</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>jbibler@encompasslending.com</t>
+          <t>kgarrison@goamplify.com</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3365,138 +3373,130 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>512-587-9500</t>
+          <t>512-836-5901</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
+          <t>company exec (local-HQ shop) | apollo (credit spent)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Residential Wholesale Mortgage</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Steve Ferguson</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Branch manager</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>steve@rwmloans.com</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>512-913-7566</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>BOK Financial Mortgage</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Corey Enlow</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>no email found</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>844-517-3308</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>no title given</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Security State Bank &amp; Trust</t>
+          <t>Encompass Lending Group</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Tim Craig</t>
+          <t>Josh Bibler</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Branch President, Liberty Hill</t>
+          <t>Regional VP</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>tcraig@ssbtexas.com</t>
+          <t>jbibler@encompasslending.com</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>from your list</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>512-263-1600</t>
+          <t>512-587-9500</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Security State Bank &amp; Trust</t>
+          <t>Residential Wholesale Mortgage</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Brian Thibodeaux</t>
+          <t>Steve Ferguson</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Branch president, Dripping Springs</t>
+          <t>Branch manager</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>bthibodeaux@ssbtexas.com</t>
+          <t>steve@rwmloans.com</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>from your list</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>512-263-1600</t>
+          <t>512-913-7566</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>local market leader / branch decision-maker</t>
+          <t>local market leader / branch decision-maker | apollo (credit spent)</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Donna Hensley</t>
+          <t>Tim Craig</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Branch president, Lago Vista</t>
+          <t>Branch President, Liberty Hill</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>dhensley@ssbtexas.com</t>
+          <t>tcraig@ssbtexas.com</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3555,17 +3555,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Joe David Sherrod</t>
+          <t>Brian Thibodeaux</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Branch president, Spicewood (Paleface, Bee Cave)</t>
+          <t>Branch president, Dripping Springs</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>jsherrod@ssbtexas.com</t>
+          <t>bthibodeaux@ssbtexas.com</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3587,47 +3587,131 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Security State Bank &amp; Trust</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Donna Hensley</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Branch president, Lago Vista</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>dhensley@ssbtexas.com</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>512-263-1600</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Security State Bank &amp; Trust</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Joe David Sherrod</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Branch president, Spicewood (Paleface, Bee Cave)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>jsherrod@ssbtexas.com</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>from your list</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>512-263-1600</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>local market leader / branch decision-maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Canopy Mortgage</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>E. Lee Smith</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Branch manager</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>esmith@canopymortgage.com</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>found by pattern test</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>512-598-9093</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>local market leader / branch decision-maker | NeverBounce pattern test, no Apollo credit</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H77"/>
+  <autoFilter ref="A1:H79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3638,14 +3722,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3666,11 +3749,6 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>Phone</t>
         </is>
       </c>
@@ -3678,81 +3756,66 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>DHI Mortgage Co. Ltd.</t>
+          <t>Fairway Independent Mortgage Corp. - Round Rock</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Eddie Garza De Haro</t>
+          <t>Steve Jacobson</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>branch sales manager</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>dhimortgage.com</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>512-502-0545</t>
+          <t>512-776-1420</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage Corp. - Round Rock</t>
+          <t>M/I Financial LLC</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Steve Jacobson</t>
+          <t>Norm Lajewski</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Branch manager</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>fairway.com</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>512-776-1420</t>
+          <t>512-770-8440</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>M/I Financial LLC</t>
+          <t>Bank of America Home Loans</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Norm Lajewski</t>
+          <t>Cindy Chism</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Branch manager</t>
+          <t>SVP-Austin home loans manager</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>mihomes.com</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>512-770-8440</t>
+          <t>512-691-0751</t>
         </is>
       </c>
     </row>
@@ -3764,20 +3827,15 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Cindy Chism</t>
+          <t>David Bader</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>SVP-Austin home loans manager</t>
+          <t>Austin president</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>bankofamerica.com</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>512-691-0751</t>
         </is>
@@ -3786,139 +3844,36 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Bank of America Home Loans</t>
+          <t>Wells Fargo Bank NA</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>David Bader</t>
+          <t>Ben Murray</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Austin president</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>bankofamerica.com</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>512-691-0751</t>
-        </is>
-      </c>
+          <t>SVP/regional executive, branch banking</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Wells Fargo Bank NA</t>
+          <t>BOK Financial Mortgage</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ben Murray</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>SVP/regional executive, branch banking</t>
-        </is>
-      </c>
+          <t>Corey Enlow</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>wellsfargo.com</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>BOK Financial Mortgage</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Corey Enlow</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>bokfinancial.com</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
           <t>844-517-3308</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="118" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>122 contacts in, 76 kept across 41 companies. 69 now have an email; 7 still do not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>8 Apollo credits and 85 NeverBounce credits spent. Apollo balance untouched otherwise; NeverBounce is at 710.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Loan officers were kept on purpose. Residential LOs are commission-based and buy their own marketing, so a producer can be a better prospect than their branch manager - the opposite of how I treated bank VPs and accounting-firm Directors on your other lists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Rows marked 'predicted (not verified)' were built from a format confirmed elsewhere at that company. Donald Grobowsky at Cadence is the only one - David Grove's verified address confirmed the first.last pattern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Rows found by 'NeverBounce pattern test' were guessed and then confirmed to be live mailboxes. Treat them as real but not Apollo-verified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>The 8 still missing are mostly at very large banks (Bank of America, Wells Fargo, BOK) where Apollo has no record under that name. Their phone numbers are in your list - these are call-first targets, not email targets.</t>
         </is>
       </c>
     </row>
